--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Demo_models\Demo_models\TIM-LEAF 080626\TIM-LEAF 080626\tim-leaf 080626\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D7E432-BBD3-4827-B824-DED810952E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8EB4EE-A3D7-4897-AE5E-07DE283C3877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="-16310" windowWidth="29020" windowHeight="15700" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="28" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="173">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -642,6 +642,15 @@
   </si>
   <si>
     <t>P24</t>
+  </si>
+  <si>
+    <t>P53</t>
+  </si>
+  <si>
+    <t>IMP*Z,-IMPDUCZ</t>
+  </si>
+  <si>
+    <t>P54</t>
   </si>
 </sst>
 </file>
@@ -846,7 +855,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -916,6 +925,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1044,7 +1059,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1155,6 +1170,7 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1164,6 +1180,7 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{98700215-67AF-41D1-9F9B-98379AE9DCA7}"/>
@@ -4012,18 +4029,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3D08AF-561B-4741-93FB-876D250B4223}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="21.6328125" style="42" customWidth="1"/>
-    <col min="5" max="6" width="14.08984375" style="42" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" style="42" customWidth="1"/>
-    <col min="8" max="10" width="8.08984375" style="42" customWidth="1"/>
-    <col min="11" max="11" width="9.6328125" style="42" customWidth="1"/>
-    <col min="12" max="12" width="8.08984375" style="42" customWidth="1"/>
+    <col min="1" max="4" width="21.54296875" style="42" customWidth="1"/>
+    <col min="5" max="6" width="14.1796875" style="42" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" style="42" customWidth="1"/>
+    <col min="8" max="10" width="8.1796875" style="42" customWidth="1"/>
+    <col min="11" max="11" width="9.54296875" style="42" customWidth="1"/>
+    <col min="12" max="12" width="8.1796875" style="42" customWidth="1"/>
     <col min="13" max="13" width="10" style="42" customWidth="1"/>
     <col min="14" max="14" width="11.453125" style="42" customWidth="1"/>
     <col min="15" max="15" width="13.453125" style="42" customWidth="1"/>
-    <col min="16" max="16384" width="8.90625" style="42"/>
+    <col min="16" max="16384" width="8.81640625" style="42"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.35">
@@ -4447,12 +4464,12 @@
       <c r="Z15" s="41"/>
     </row>
     <row r="16" spans="1:26" ht="102.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="58" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
       <c r="E16" s="43"/>
       <c r="F16" s="43"/>
       <c r="G16" s="44"/>
@@ -4536,11 +4553,11 @@
       <c r="A19" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
       <c r="E19" s="49"/>
       <c r="F19" s="49"/>
       <c r="G19" s="50"/>
@@ -4568,11 +4585,11 @@
       <c r="A20" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
       <c r="E20" s="49"/>
       <c r="F20" s="49"/>
       <c r="G20" s="50"/>
@@ -4660,11 +4677,11 @@
       <c r="A23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="56" t="s">
+      <c r="B23" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
       <c r="E23" s="41"/>
       <c r="F23" s="41"/>
       <c r="G23" s="41"/>
@@ -4750,11 +4767,11 @@
       <c r="A26" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
       <c r="E26" s="41"/>
       <c r="F26" s="41"/>
       <c r="G26" s="41"/>
@@ -4870,11 +4887,11 @@
       <c r="A30" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="B30" s="58" t="s">
+      <c r="B30" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
       <c r="E30" s="53"/>
       <c r="F30" s="53"/>
       <c r="G30" s="41"/>
@@ -4902,11 +4919,11 @@
       <c r="A31" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="B31" s="56" t="s">
+      <c r="B31" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
       <c r="E31" s="53"/>
       <c r="F31" s="53"/>
       <c r="G31" s="41"/>
@@ -6862,33 +6879,32 @@
   <dimension ref="A3:AD37"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.08984375" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" customWidth="1"/>
     <col min="4" max="4" width="8.54296875" customWidth="1"/>
     <col min="5" max="5" width="6.453125" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="5.6328125" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" customWidth="1"/>
+    <col min="7" max="7" width="5.54296875" customWidth="1"/>
+    <col min="8" max="8" width="5.81640625" customWidth="1"/>
     <col min="9" max="9" width="5.453125" customWidth="1"/>
-    <col min="10" max="11" width="5.6328125" customWidth="1"/>
+    <col min="10" max="11" width="5.54296875" customWidth="1"/>
     <col min="12" max="12" width="6.54296875" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.6328125" customWidth="1"/>
-    <col min="15" max="15" width="6.54296875" customWidth="1"/>
-    <col min="16" max="16" width="7.08984375" customWidth="1"/>
-    <col min="17" max="17" width="5.6328125" customWidth="1"/>
+    <col min="14" max="15" width="6.54296875" customWidth="1"/>
+    <col min="16" max="16" width="7.1796875" customWidth="1"/>
+    <col min="17" max="17" width="5.54296875" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="5.90625" customWidth="1"/>
+    <col min="19" max="19" width="5.81640625" customWidth="1"/>
     <col min="20" max="20" width="5.54296875" customWidth="1"/>
-    <col min="21" max="21" width="5.90625" customWidth="1"/>
-    <col min="22" max="22" width="6.6328125" customWidth="1"/>
+    <col min="21" max="21" width="5.81640625" customWidth="1"/>
+    <col min="22" max="22" width="6.54296875" customWidth="1"/>
     <col min="23" max="23" width="5" customWidth="1"/>
     <col min="24" max="24" width="7.54296875" customWidth="1"/>
-    <col min="25" max="25" width="6.6328125" customWidth="1"/>
+    <col min="25" max="25" width="6.54296875" customWidth="1"/>
     <col min="26" max="28" width="6" customWidth="1"/>
-    <col min="29" max="29" width="5.6328125" customWidth="1"/>
-    <col min="30" max="30" width="6.6328125" customWidth="1"/>
+    <col min="29" max="29" width="5.54296875" customWidth="1"/>
+    <col min="30" max="30" width="6.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7540,7 +7556,7 @@
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.453125" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
     <col min="5" max="5" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7803,41 +7819,41 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B3:V51"/>
+  <dimension ref="B3:Y75"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="9" width="13.6328125" customWidth="1"/>
+    <col min="2" max="9" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:22" ht="13" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:25" ht="13" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="11"/>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2018</v>
       </c>
     </row>
-    <row r="7" spans="2:22" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:25" ht="13" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="11"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:22" ht="13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:25" ht="13" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="11"/>
     </row>
-    <row r="12" spans="2:22" ht="13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:25" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>137</v>
       </c>
@@ -7868,38 +7884,45 @@
       <c r="K12" s="13" t="s">
         <v>169</v>
       </c>
+      <c r="L12" s="13" t="s">
+        <v>170</v>
+      </c>
       <c r="M12" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="N12" s="60"/>
+      <c r="P12" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="Q12" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="O12" s="13" t="s">
+      <c r="R12" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="P12" s="39" t="s">
+      <c r="S12" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="Q12" s="13" t="s">
+      <c r="T12" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="R12" s="39" t="s">
+      <c r="U12" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="S12" s="39" t="s">
+      <c r="V12" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="T12" s="39" t="s">
+      <c r="W12" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="U12" s="13" t="s">
+      <c r="X12" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="V12" s="13" t="s">
+      <c r="Y12" s="13" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>1</v>
       </c>
@@ -7930,48 +7953,55 @@
       <c r="K13" s="12">
         <v>1</v>
       </c>
-      <c r="M13" s="12">
+      <c r="L13" s="56">
+        <v>1</v>
+      </c>
+      <c r="M13" s="56">
+        <v>1</v>
+      </c>
+      <c r="N13" s="56"/>
+      <c r="P13" s="12">
         <f>+B4</f>
         <v>2018</v>
       </c>
-      <c r="N13" s="12">
-        <f>+M13</f>
+      <c r="Q13" s="12">
+        <f>+P13</f>
         <v>2018</v>
       </c>
-      <c r="O13" s="12">
-        <f t="shared" ref="O13:T13" si="0">+N13</f>
+      <c r="R13" s="12">
+        <f t="shared" ref="R13:W13" si="0">+Q13</f>
         <v>2018</v>
       </c>
-      <c r="P13" s="12">
+      <c r="S13" s="12">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="Q13" s="12">
+      <c r="T13" s="12">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="R13" s="12">
+      <c r="U13" s="12">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="S13" s="17">
+      <c r="V13" s="17">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="T13" s="17">
+      <c r="W13" s="17">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="U13" s="17">
-        <f t="shared" ref="U13:V13" si="1">+T13</f>
+      <c r="X13" s="17">
+        <f t="shared" ref="X13:Y13" si="1">+W13</f>
         <v>2018</v>
       </c>
-      <c r="V13" s="17">
+      <c r="Y13" s="17">
         <f t="shared" si="1"/>
         <v>2018</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B14" s="12">
         <v>1</v>
       </c>
@@ -8002,48 +8032,55 @@
       <c r="K14" s="12">
         <v>1</v>
       </c>
-      <c r="M14" s="12">
-        <f>+M13+B14</f>
+      <c r="L14" s="56">
+        <v>1</v>
+      </c>
+      <c r="M14" s="56">
+        <v>1</v>
+      </c>
+      <c r="N14" s="56"/>
+      <c r="P14" s="12">
+        <f>+P13+B14</f>
         <v>2019</v>
       </c>
-      <c r="N14" s="12">
-        <f t="shared" ref="N14:V29" si="2">+N13+C14</f>
+      <c r="Q14" s="12">
+        <f>+Q13+C14</f>
         <v>2019</v>
       </c>
-      <c r="O14" s="12">
-        <f t="shared" si="2"/>
+      <c r="R14" s="12">
+        <f>+R13+D14</f>
         <v>2022</v>
       </c>
-      <c r="P14" s="12">
-        <f t="shared" si="2"/>
+      <c r="S14" s="12">
+        <f>+S13+E14</f>
         <v>2021</v>
       </c>
-      <c r="Q14" s="12">
-        <f t="shared" si="2"/>
+      <c r="T14" s="12">
+        <f>+T13+F14</f>
         <v>2019</v>
       </c>
-      <c r="R14" s="12">
-        <f t="shared" si="2"/>
+      <c r="U14" s="12">
+        <f>+U13+G14</f>
         <v>2019</v>
       </c>
-      <c r="S14" s="17">
-        <f t="shared" si="2"/>
+      <c r="V14" s="17">
+        <f>+V13+H14</f>
         <v>2019</v>
       </c>
-      <c r="T14" s="17">
-        <f t="shared" si="2"/>
+      <c r="W14" s="17">
+        <f>+W13+I14</f>
         <v>2019</v>
       </c>
-      <c r="U14" s="17">
-        <f t="shared" si="2"/>
+      <c r="X14" s="17">
+        <f>+X13+J14</f>
         <v>2019</v>
       </c>
-      <c r="V14" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y14" s="17">
+        <f>+Y13+K14</f>
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>1</v>
       </c>
@@ -8074,48 +8111,55 @@
       <c r="K15" s="12">
         <v>1</v>
       </c>
-      <c r="M15" s="12">
-        <f t="shared" ref="M15:M17" si="3">+M14+B15</f>
+      <c r="L15" s="56">
+        <v>1</v>
+      </c>
+      <c r="M15" s="56">
+        <v>1</v>
+      </c>
+      <c r="N15" s="56"/>
+      <c r="P15" s="12">
+        <f t="shared" ref="P15:P17" si="2">+P14+B15</f>
         <v>2020</v>
       </c>
-      <c r="N15" s="12">
-        <f t="shared" si="2"/>
+      <c r="Q15" s="12">
+        <f>+Q14+C15</f>
         <v>2020</v>
       </c>
-      <c r="O15" s="12">
-        <f t="shared" si="2"/>
+      <c r="R15" s="12">
+        <f>+R14+D15</f>
         <v>2027</v>
       </c>
-      <c r="P15" s="12">
-        <f t="shared" si="2"/>
+      <c r="S15" s="12">
+        <f>+S14+E15</f>
         <v>2022</v>
       </c>
-      <c r="Q15" s="12">
-        <f t="shared" si="2"/>
+      <c r="T15" s="12">
+        <f>+T14+F15</f>
         <v>2020</v>
       </c>
-      <c r="R15" s="12">
-        <f t="shared" si="2"/>
+      <c r="U15" s="12">
+        <f>+U14+G15</f>
         <v>2020</v>
       </c>
-      <c r="S15" s="17">
-        <f t="shared" si="2"/>
+      <c r="V15" s="17">
+        <f>+V14+H15</f>
         <v>2020</v>
       </c>
-      <c r="T15" s="17">
-        <f t="shared" si="2"/>
+      <c r="W15" s="17">
+        <f>+W14+I15</f>
         <v>2020</v>
       </c>
-      <c r="U15" s="17">
-        <f t="shared" si="2"/>
+      <c r="X15" s="17">
+        <f>+X14+J15</f>
         <v>2020</v>
       </c>
-      <c r="V15" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y15" s="17">
+        <f>+Y14+K15</f>
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B16" s="12">
         <v>20</v>
       </c>
@@ -8146,48 +8190,55 @@
       <c r="K16" s="12">
         <v>1</v>
       </c>
-      <c r="M16" s="12">
-        <f t="shared" si="3"/>
-        <v>2040</v>
-      </c>
-      <c r="N16" s="12">
-        <f t="shared" si="2"/>
-        <v>2021</v>
-      </c>
-      <c r="O16" s="12">
-        <f t="shared" si="2"/>
-        <v>2032</v>
-      </c>
+      <c r="L16" s="56">
+        <v>1</v>
+      </c>
+      <c r="M16" s="56">
+        <v>1</v>
+      </c>
+      <c r="N16" s="56"/>
       <c r="P16" s="12">
         <f t="shared" si="2"/>
+        <v>2040</v>
+      </c>
+      <c r="Q16" s="12">
+        <f>+Q15+C16</f>
+        <v>2021</v>
+      </c>
+      <c r="R16" s="12">
+        <f>+R15+D16</f>
+        <v>2032</v>
+      </c>
+      <c r="S16" s="12">
+        <f>+S15+E16</f>
         <v>2027</v>
       </c>
-      <c r="Q16" s="12">
-        <f t="shared" si="2"/>
+      <c r="T16" s="12">
+        <f>+T15+F16</f>
         <v>2021</v>
       </c>
-      <c r="R16" s="12">
-        <f t="shared" si="2"/>
+      <c r="U16" s="12">
+        <f>+U15+G16</f>
         <v>2021</v>
       </c>
-      <c r="S16" s="17">
-        <f t="shared" si="2"/>
+      <c r="V16" s="17">
+        <f>+V15+H16</f>
         <v>2021</v>
       </c>
-      <c r="T16" s="17">
-        <f t="shared" si="2"/>
+      <c r="W16" s="17">
+        <f>+W15+I16</f>
         <v>2021</v>
       </c>
-      <c r="U16" s="17">
-        <f t="shared" si="2"/>
+      <c r="X16" s="17">
+        <f>+X15+J16</f>
         <v>2021</v>
       </c>
-      <c r="V16" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y16" s="17">
+        <f>+Y15+K16</f>
         <v>2021</v>
       </c>
     </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B17" s="12">
         <v>20</v>
       </c>
@@ -8218,48 +8269,55 @@
       <c r="K17" s="12">
         <v>1</v>
       </c>
-      <c r="M17" s="12">
-        <f t="shared" si="3"/>
-        <v>2060</v>
-      </c>
-      <c r="N17" s="12">
-        <f t="shared" si="2"/>
-        <v>2022</v>
-      </c>
-      <c r="O17" s="12">
-        <f t="shared" si="2"/>
-        <v>2037</v>
-      </c>
+      <c r="L17" s="56">
+        <v>1</v>
+      </c>
+      <c r="M17" s="56">
+        <v>1</v>
+      </c>
+      <c r="N17" s="56"/>
       <c r="P17" s="12">
         <f t="shared" si="2"/>
+        <v>2060</v>
+      </c>
+      <c r="Q17" s="12">
+        <f>+Q16+C17</f>
+        <v>2022</v>
+      </c>
+      <c r="R17" s="12">
+        <f>+R16+D17</f>
+        <v>2037</v>
+      </c>
+      <c r="S17" s="12">
+        <f>+S16+E17</f>
         <v>2032</v>
       </c>
-      <c r="Q17" s="12">
-        <f t="shared" si="2"/>
+      <c r="T17" s="12">
+        <f>+T16+F17</f>
         <v>2022</v>
       </c>
-      <c r="R17" s="12">
-        <f t="shared" si="2"/>
+      <c r="U17" s="12">
+        <f>+U16+G17</f>
         <v>2022</v>
       </c>
-      <c r="S17" s="17">
-        <f t="shared" si="2"/>
+      <c r="V17" s="17">
+        <f>+V16+H17</f>
         <v>2022</v>
       </c>
-      <c r="T17" s="17">
-        <f t="shared" si="2"/>
+      <c r="W17" s="17">
+        <f>+W16+I17</f>
         <v>2022</v>
       </c>
-      <c r="U17" s="17">
-        <f t="shared" si="2"/>
+      <c r="X17" s="17">
+        <f>+X16+J17</f>
         <v>2022</v>
       </c>
-      <c r="V17" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y17" s="17">
+        <f>+Y16+K17</f>
         <v>2022</v>
       </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C18" s="12">
         <v>5</v>
       </c>
@@ -8287,44 +8345,51 @@
       <c r="K18" s="12">
         <v>1</v>
       </c>
-      <c r="N18" s="12">
-        <f t="shared" si="2"/>
+      <c r="L18" s="56">
+        <v>1</v>
+      </c>
+      <c r="M18" s="56">
+        <v>1</v>
+      </c>
+      <c r="N18" s="56"/>
+      <c r="Q18" s="12">
+        <f>+Q17+C18</f>
         <v>2027</v>
       </c>
-      <c r="O18" s="12">
-        <f t="shared" si="2"/>
+      <c r="R18" s="12">
+        <f>+R17+D18</f>
         <v>2042</v>
       </c>
-      <c r="P18" s="12">
-        <f t="shared" si="2"/>
+      <c r="S18" s="12">
+        <f>+S17+E18</f>
         <v>2037</v>
       </c>
-      <c r="Q18" s="12">
-        <f t="shared" si="2"/>
+      <c r="T18" s="12">
+        <f>+T17+F18</f>
         <v>2027</v>
       </c>
-      <c r="R18" s="12">
-        <f t="shared" si="2"/>
+      <c r="U18" s="12">
+        <f>+U17+G18</f>
         <v>2023</v>
       </c>
-      <c r="S18" s="17">
-        <f t="shared" si="2"/>
+      <c r="V18" s="17">
+        <f>+V17+H18</f>
         <v>2023</v>
       </c>
-      <c r="T18" s="17">
-        <f t="shared" si="2"/>
+      <c r="W18" s="17">
+        <f>+W17+I18</f>
         <v>2023</v>
       </c>
-      <c r="U18" s="17">
-        <f t="shared" si="2"/>
+      <c r="X18" s="17">
+        <f>+X17+J18</f>
         <v>2023</v>
       </c>
-      <c r="V18" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y18" s="17">
+        <f>+Y17+K18</f>
         <v>2023</v>
       </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C19" s="12">
         <v>45</v>
       </c>
@@ -8352,44 +8417,51 @@
       <c r="K19" s="12">
         <v>1</v>
       </c>
-      <c r="N19" s="12">
-        <f t="shared" si="2"/>
+      <c r="L19" s="56">
+        <v>1</v>
+      </c>
+      <c r="M19" s="56">
+        <v>1</v>
+      </c>
+      <c r="N19" s="56"/>
+      <c r="Q19" s="12">
+        <f>+Q18+C19</f>
         <v>2072</v>
       </c>
-      <c r="O19" s="12">
-        <f t="shared" si="2"/>
+      <c r="R19" s="12">
+        <f>+R18+D19</f>
         <v>2047</v>
       </c>
-      <c r="P19" s="12">
-        <f t="shared" si="2"/>
+      <c r="S19" s="12">
+        <f>+S18+E19</f>
         <v>2042</v>
       </c>
-      <c r="Q19" s="12">
-        <f t="shared" si="2"/>
+      <c r="T19" s="12">
+        <f>+T18+F19</f>
         <v>2032</v>
       </c>
-      <c r="R19" s="12">
-        <f t="shared" si="2"/>
+      <c r="U19" s="12">
+        <f>+U18+G19</f>
         <v>2024</v>
       </c>
-      <c r="S19" s="17">
-        <f t="shared" si="2"/>
+      <c r="V19" s="17">
+        <f>+V18+H19</f>
         <v>2024</v>
       </c>
-      <c r="T19" s="17">
-        <f t="shared" si="2"/>
+      <c r="W19" s="17">
+        <f>+W18+I19</f>
         <v>2024</v>
       </c>
-      <c r="U19" s="17">
-        <f t="shared" si="2"/>
+      <c r="X19" s="17">
+        <f>+X18+J19</f>
         <v>2024</v>
       </c>
-      <c r="V19" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y19" s="17">
+        <f>+Y18+K19</f>
         <v>2024</v>
       </c>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C20" s="12">
         <v>25</v>
       </c>
@@ -8417,44 +8489,51 @@
       <c r="K20" s="12">
         <v>1</v>
       </c>
-      <c r="N20" s="12">
-        <f t="shared" si="2"/>
+      <c r="L20" s="56">
+        <v>1</v>
+      </c>
+      <c r="M20" s="56">
+        <v>1</v>
+      </c>
+      <c r="N20" s="56"/>
+      <c r="Q20" s="12">
+        <f>+Q19+C20</f>
         <v>2097</v>
       </c>
-      <c r="O20" s="12">
-        <f t="shared" si="2"/>
+      <c r="R20" s="12">
+        <f>+R19+D20</f>
         <v>2052</v>
       </c>
-      <c r="P20" s="12">
-        <f t="shared" si="2"/>
+      <c r="S20" s="12">
+        <f>+S19+E20</f>
         <v>2047</v>
       </c>
-      <c r="Q20" s="12">
-        <f t="shared" si="2"/>
+      <c r="T20" s="12">
+        <f>+T19+F20</f>
         <v>2037</v>
       </c>
-      <c r="R20" s="12">
-        <f t="shared" si="2"/>
+      <c r="U20" s="12">
+        <f>+U19+G20</f>
         <v>2025</v>
       </c>
-      <c r="S20" s="17">
-        <f t="shared" si="2"/>
+      <c r="V20" s="17">
+        <f>+V19+H20</f>
         <v>2025</v>
       </c>
-      <c r="T20" s="17">
-        <f t="shared" si="2"/>
+      <c r="W20" s="17">
+        <f>+W19+I20</f>
         <v>2025</v>
       </c>
-      <c r="U20" s="17">
-        <f t="shared" si="2"/>
+      <c r="X20" s="17">
+        <f>+X19+J20</f>
         <v>2025</v>
       </c>
-      <c r="V20" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y20" s="17">
+        <f>+Y19+K20</f>
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C21" s="12">
         <v>5</v>
       </c>
@@ -8482,44 +8561,51 @@
       <c r="K21" s="12">
         <v>3</v>
       </c>
-      <c r="N21" s="12">
-        <f t="shared" si="2"/>
+      <c r="L21" s="56">
+        <v>1</v>
+      </c>
+      <c r="M21" s="56">
+        <v>1</v>
+      </c>
+      <c r="N21" s="56"/>
+      <c r="Q21" s="12">
+        <f>+Q20+C21</f>
         <v>2102</v>
       </c>
-      <c r="O21" s="12">
-        <f t="shared" si="2"/>
+      <c r="R21" s="12">
+        <f>+R20+D21</f>
         <v>2057</v>
       </c>
-      <c r="P21" s="12">
-        <f t="shared" si="2"/>
+      <c r="S21" s="12">
+        <f>+S20+E21</f>
         <v>2052</v>
       </c>
-      <c r="Q21" s="12">
-        <f t="shared" si="2"/>
+      <c r="T21" s="12">
+        <f>+T20+F21</f>
         <v>2042</v>
       </c>
-      <c r="R21" s="12">
-        <f t="shared" si="2"/>
+      <c r="U21" s="12">
+        <f>+U20+G21</f>
         <v>2026</v>
       </c>
-      <c r="S21" s="17">
-        <f t="shared" si="2"/>
+      <c r="V21" s="17">
+        <f>+V20+H21</f>
         <v>2026</v>
       </c>
-      <c r="T21" s="17">
-        <f t="shared" si="2"/>
+      <c r="W21" s="17">
+        <f>+W20+I21</f>
         <v>2026</v>
       </c>
-      <c r="U21" s="17">
-        <f>+U20+J21-5</f>
+      <c r="X21" s="17">
+        <f>+X20+J21-5</f>
         <v>2030</v>
       </c>
-      <c r="V21" s="17">
-        <f>+V20+K21-1</f>
+      <c r="Y21" s="17">
+        <f>+Y20+K21-1</f>
         <v>2027</v>
       </c>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="D22" s="12">
         <v>5</v>
       </c>
@@ -8544,40 +8630,47 @@
       <c r="K22" s="12">
         <v>4</v>
       </c>
-      <c r="O22" s="12">
-        <f t="shared" si="2"/>
+      <c r="L22" s="56">
+        <v>1</v>
+      </c>
+      <c r="M22" s="56">
+        <v>1</v>
+      </c>
+      <c r="N22" s="56"/>
+      <c r="R22" s="12">
+        <f>+R21+D22</f>
         <v>2062</v>
       </c>
-      <c r="P22" s="12">
-        <f t="shared" si="2"/>
+      <c r="S22" s="12">
+        <f>+S21+E22</f>
         <v>2057</v>
       </c>
-      <c r="Q22" s="12">
-        <f t="shared" si="2"/>
+      <c r="T22" s="12">
+        <f>+T21+F22</f>
         <v>2047</v>
       </c>
-      <c r="R22" s="12">
-        <f t="shared" si="2"/>
+      <c r="U22" s="12">
+        <f>+U21+G22</f>
         <v>2027</v>
       </c>
-      <c r="S22" s="17">
-        <f t="shared" si="2"/>
+      <c r="V22" s="17">
+        <f>+V21+H22</f>
         <v>2027</v>
       </c>
-      <c r="T22" s="17">
-        <f t="shared" si="2"/>
+      <c r="W22" s="17">
+        <f>+W21+I22</f>
         <v>2027</v>
       </c>
-      <c r="U22" s="17">
-        <f t="shared" si="2"/>
+      <c r="X22" s="17">
+        <f>+X21+J22</f>
         <v>2040</v>
       </c>
-      <c r="V22" s="17">
-        <f>+V21+K22-2</f>
+      <c r="Y22" s="17">
+        <f>+Y21+K22-2</f>
         <v>2029</v>
       </c>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
       <c r="D23" s="12">
         <v>5</v>
       </c>
@@ -8602,40 +8695,47 @@
       <c r="K23" s="12">
         <v>5</v>
       </c>
-      <c r="O23" s="12">
-        <f t="shared" si="2"/>
+      <c r="L23" s="56">
+        <v>1</v>
+      </c>
+      <c r="M23" s="56">
+        <v>1</v>
+      </c>
+      <c r="N23" s="56"/>
+      <c r="R23" s="12">
+        <f>+R22+D23</f>
         <v>2067</v>
       </c>
-      <c r="P23" s="12">
-        <f t="shared" si="2"/>
+      <c r="S23" s="12">
+        <f>+S22+E23</f>
         <v>2062</v>
       </c>
-      <c r="Q23" s="12">
-        <f t="shared" si="2"/>
+      <c r="T23" s="12">
+        <f>+T22+F23</f>
         <v>2052</v>
       </c>
-      <c r="R23" s="12">
-        <f t="shared" si="2"/>
+      <c r="U23" s="12">
+        <f>+U22+G23</f>
         <v>2028</v>
       </c>
-      <c r="S23" s="17">
-        <f t="shared" si="2"/>
+      <c r="V23" s="17">
+        <f>+V22+H23</f>
         <v>2028</v>
       </c>
-      <c r="T23" s="17">
-        <f t="shared" si="2"/>
+      <c r="W23" s="17">
+        <f>+W22+I23</f>
         <v>2028</v>
       </c>
-      <c r="U23" s="17">
-        <f t="shared" si="2"/>
+      <c r="X23" s="17">
+        <f>+X22+J23</f>
         <v>2050</v>
       </c>
-      <c r="V23" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y23" s="17">
+        <f t="shared" ref="Y23:Y29" si="3">+Y22+K23</f>
         <v>2034</v>
       </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="D24" s="12">
         <v>5</v>
       </c>
@@ -8660,40 +8760,47 @@
       <c r="K24" s="12">
         <v>5</v>
       </c>
-      <c r="O24" s="12">
-        <f t="shared" si="2"/>
+      <c r="L24" s="56">
+        <v>1</v>
+      </c>
+      <c r="M24" s="56">
+        <v>1</v>
+      </c>
+      <c r="N24" s="56"/>
+      <c r="R24" s="12">
+        <f>+R23+D24</f>
         <v>2072</v>
       </c>
-      <c r="P24" s="12">
-        <f t="shared" si="2"/>
+      <c r="S24" s="12">
+        <f>+S23+E24</f>
         <v>2067</v>
       </c>
-      <c r="Q24" s="12">
-        <f t="shared" si="2"/>
+      <c r="T24" s="12">
+        <f>+T23+F24</f>
         <v>2057</v>
       </c>
-      <c r="R24" s="12">
-        <f t="shared" si="2"/>
+      <c r="U24" s="12">
+        <f>+U23+G24</f>
         <v>2029</v>
       </c>
-      <c r="S24" s="17">
-        <f t="shared" si="2"/>
+      <c r="V24" s="17">
+        <f>+V23+H24</f>
         <v>2029</v>
       </c>
-      <c r="T24" s="17">
-        <f t="shared" si="2"/>
+      <c r="W24" s="17">
+        <f>+W23+I24</f>
         <v>2029</v>
       </c>
-      <c r="U24" s="17">
-        <f t="shared" si="2"/>
+      <c r="X24" s="17">
+        <f>+X23+J24</f>
         <v>2060</v>
       </c>
-      <c r="V24" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y24" s="17">
+        <f t="shared" si="3"/>
         <v>2039</v>
       </c>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E25" s="12">
         <v>5</v>
       </c>
@@ -8715,36 +8822,43 @@
       <c r="K25" s="12">
         <v>5</v>
       </c>
-      <c r="P25" s="12">
-        <f t="shared" si="2"/>
+      <c r="L25" s="56">
+        <v>1</v>
+      </c>
+      <c r="M25" s="56">
+        <v>1</v>
+      </c>
+      <c r="N25" s="56"/>
+      <c r="S25" s="12">
+        <f>+S24+E25</f>
         <v>2072</v>
       </c>
-      <c r="Q25" s="12">
-        <f t="shared" si="2"/>
+      <c r="T25" s="12">
+        <f>+T24+F25</f>
         <v>2062</v>
       </c>
-      <c r="R25" s="12">
-        <f t="shared" si="2"/>
+      <c r="U25" s="12">
+        <f>+U24+G25</f>
         <v>2030</v>
       </c>
-      <c r="S25" s="17">
-        <f t="shared" si="2"/>
+      <c r="V25" s="17">
+        <f>+V24+H25</f>
         <v>2030</v>
       </c>
-      <c r="T25" s="17">
-        <f t="shared" si="2"/>
+      <c r="W25" s="17">
+        <f>+W24+I25</f>
         <v>2030</v>
       </c>
-      <c r="U25" s="17">
-        <f t="shared" si="2"/>
+      <c r="X25" s="17">
+        <f>+X24+J25</f>
         <v>2070</v>
       </c>
-      <c r="V25" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y25" s="17">
+        <f t="shared" si="3"/>
         <v>2044</v>
       </c>
     </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="F26" s="12">
         <v>5</v>
       </c>
@@ -8763,32 +8877,39 @@
       <c r="K26" s="12">
         <v>5</v>
       </c>
-      <c r="Q26" s="12">
-        <f t="shared" si="2"/>
+      <c r="L26" s="56">
+        <v>1</v>
+      </c>
+      <c r="M26" s="56">
+        <v>1</v>
+      </c>
+      <c r="N26" s="56"/>
+      <c r="T26" s="12">
+        <f>+T25+F26</f>
         <v>2067</v>
       </c>
-      <c r="R26" s="12">
-        <f t="shared" si="2"/>
+      <c r="U26" s="12">
+        <f>+U25+G26</f>
         <v>2031</v>
       </c>
-      <c r="S26" s="17">
-        <f t="shared" si="2"/>
+      <c r="V26" s="17">
+        <f>+V25+H26</f>
         <v>2031</v>
       </c>
-      <c r="T26" s="17">
-        <f t="shared" si="2"/>
+      <c r="W26" s="17">
+        <f>+W25+I26</f>
         <v>2031</v>
       </c>
-      <c r="U26" s="17">
-        <f t="shared" si="2"/>
+      <c r="X26" s="17">
+        <f>+X25+J26</f>
         <v>2080</v>
       </c>
-      <c r="V26" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y26" s="17">
+        <f t="shared" si="3"/>
         <v>2049</v>
       </c>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="F27" s="12">
         <v>5</v>
       </c>
@@ -8807,32 +8928,39 @@
       <c r="K27" s="12">
         <v>5</v>
       </c>
-      <c r="Q27" s="12">
-        <f t="shared" si="2"/>
+      <c r="L27" s="56">
+        <v>1</v>
+      </c>
+      <c r="M27" s="56">
+        <v>1</v>
+      </c>
+      <c r="N27" s="56"/>
+      <c r="T27" s="12">
+        <f>+T26+F27</f>
         <v>2072</v>
       </c>
-      <c r="R27" s="12">
-        <f t="shared" si="2"/>
+      <c r="U27" s="12">
+        <f>+U26+G27</f>
         <v>2032</v>
       </c>
-      <c r="S27" s="17">
-        <f t="shared" si="2"/>
+      <c r="V27" s="17">
+        <f>+V26+H27</f>
         <v>2032</v>
       </c>
-      <c r="T27" s="17">
-        <f t="shared" si="2"/>
+      <c r="W27" s="17">
+        <f>+W26+I27</f>
         <v>2032</v>
       </c>
-      <c r="U27" s="17">
-        <f t="shared" si="2"/>
+      <c r="X27" s="17">
+        <f>+X26+J27</f>
         <v>2090</v>
       </c>
-      <c r="V27" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y27" s="17">
+        <f t="shared" si="3"/>
         <v>2054</v>
       </c>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G28" s="12">
         <v>5</v>
       </c>
@@ -8848,28 +8976,35 @@
       <c r="K28" s="12">
         <v>5</v>
       </c>
-      <c r="R28" s="12">
-        <f t="shared" si="2"/>
+      <c r="L28" s="56">
+        <v>1</v>
+      </c>
+      <c r="M28" s="56">
+        <v>1</v>
+      </c>
+      <c r="N28" s="56"/>
+      <c r="U28" s="12">
+        <f>+U27+G28</f>
         <v>2037</v>
       </c>
-      <c r="S28" s="17">
-        <f t="shared" si="2"/>
+      <c r="V28" s="17">
+        <f>+V27+H28</f>
         <v>2033</v>
       </c>
-      <c r="T28" s="17">
-        <f t="shared" si="2"/>
+      <c r="W28" s="17">
+        <f>+W27+I28</f>
         <v>2033</v>
       </c>
-      <c r="U28" s="17">
-        <f t="shared" si="2"/>
+      <c r="X28" s="17">
+        <f>+X27+J28</f>
         <v>2100</v>
       </c>
-      <c r="V28" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y28" s="17">
+        <f t="shared" si="3"/>
         <v>2059</v>
       </c>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G29" s="12">
         <v>5</v>
       </c>
@@ -8882,24 +9017,31 @@
       <c r="K29" s="12">
         <v>5</v>
       </c>
-      <c r="R29" s="12">
-        <f t="shared" si="2"/>
+      <c r="L29" s="56">
+        <v>1</v>
+      </c>
+      <c r="M29" s="56">
+        <v>1</v>
+      </c>
+      <c r="N29" s="56"/>
+      <c r="U29" s="12">
+        <f>+U28+G29</f>
         <v>2042</v>
       </c>
-      <c r="S29" s="17">
-        <f t="shared" si="2"/>
+      <c r="V29" s="17">
+        <f>+V28+H29</f>
         <v>2034</v>
       </c>
-      <c r="T29" s="17">
-        <f t="shared" si="2"/>
+      <c r="W29" s="17">
+        <f>+W28+I29</f>
         <v>2034</v>
       </c>
-      <c r="V29" s="17">
-        <f t="shared" si="2"/>
+      <c r="Y29" s="17">
+        <f t="shared" si="3"/>
         <v>2064</v>
       </c>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G30" s="12">
         <v>5</v>
       </c>
@@ -8912,24 +9054,31 @@
       <c r="K30" s="12">
         <v>5</v>
       </c>
-      <c r="R30" s="12">
-        <f t="shared" ref="R30:T45" si="4">+R29+G30</f>
+      <c r="L30" s="56">
+        <v>1</v>
+      </c>
+      <c r="M30" s="56">
+        <v>1</v>
+      </c>
+      <c r="N30" s="56"/>
+      <c r="U30" s="12">
+        <f>+U29+G30</f>
         <v>2047</v>
       </c>
-      <c r="S30" s="17">
-        <f t="shared" si="4"/>
+      <c r="V30" s="17">
+        <f>+V29+H30</f>
         <v>2035</v>
       </c>
-      <c r="T30" s="17">
-        <f t="shared" si="4"/>
+      <c r="W30" s="17">
+        <f>+W29+I30</f>
         <v>2035</v>
       </c>
-      <c r="V30" s="17">
-        <f t="shared" ref="V30:V35" si="5">+V29+K30</f>
+      <c r="Y30" s="17">
+        <f t="shared" ref="Y30:Y35" si="4">+Y29+K30</f>
         <v>2069</v>
       </c>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G31" s="12">
         <v>5</v>
       </c>
@@ -8942,24 +9091,31 @@
       <c r="K31" s="12">
         <v>5</v>
       </c>
-      <c r="R31" s="12">
+      <c r="L31" s="56">
+        <v>1</v>
+      </c>
+      <c r="M31" s="56">
+        <v>1</v>
+      </c>
+      <c r="N31" s="56"/>
+      <c r="U31" s="12">
+        <f>+U30+G31</f>
+        <v>2052</v>
+      </c>
+      <c r="V31" s="17">
+        <f>+V30+H31</f>
+        <v>2036</v>
+      </c>
+      <c r="W31" s="17">
+        <f>+W30+I31</f>
+        <v>2036</v>
+      </c>
+      <c r="Y31" s="17">
         <f t="shared" si="4"/>
-        <v>2052</v>
-      </c>
-      <c r="S31" s="17">
-        <f t="shared" si="4"/>
-        <v>2036</v>
-      </c>
-      <c r="T31" s="17">
-        <f t="shared" si="4"/>
-        <v>2036</v>
-      </c>
-      <c r="V31" s="17">
-        <f t="shared" si="5"/>
         <v>2074</v>
       </c>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G32" s="12">
         <v>5</v>
       </c>
@@ -8972,24 +9128,31 @@
       <c r="K32" s="12">
         <v>5</v>
       </c>
-      <c r="R32" s="12">
+      <c r="L32" s="56">
+        <v>1</v>
+      </c>
+      <c r="M32" s="56">
+        <v>1</v>
+      </c>
+      <c r="N32" s="56"/>
+      <c r="U32" s="12">
+        <f>+U31+G32</f>
+        <v>2057</v>
+      </c>
+      <c r="V32" s="17">
+        <f>+V31+H32</f>
+        <v>2037</v>
+      </c>
+      <c r="W32" s="17">
+        <f>+W31+I32</f>
+        <v>2037</v>
+      </c>
+      <c r="Y32" s="17">
         <f t="shared" si="4"/>
-        <v>2057</v>
-      </c>
-      <c r="S32" s="17">
-        <f t="shared" si="4"/>
-        <v>2037</v>
-      </c>
-      <c r="T32" s="17">
-        <f t="shared" si="4"/>
-        <v>2037</v>
-      </c>
-      <c r="V32" s="17">
-        <f t="shared" si="5"/>
         <v>2079</v>
       </c>
     </row>
-    <row r="33" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:25" x14ac:dyDescent="0.25">
       <c r="G33" s="12">
         <v>5</v>
       </c>
@@ -9002,24 +9165,31 @@
       <c r="K33" s="12">
         <v>5</v>
       </c>
-      <c r="R33" s="12">
+      <c r="L33" s="56">
+        <v>1</v>
+      </c>
+      <c r="M33" s="56">
+        <v>1</v>
+      </c>
+      <c r="N33" s="56"/>
+      <c r="U33" s="12">
+        <f>+U32+G33</f>
+        <v>2062</v>
+      </c>
+      <c r="V33" s="17">
+        <f>+V32+H33</f>
+        <v>2038</v>
+      </c>
+      <c r="W33" s="17">
+        <f>+W32+I33</f>
+        <v>2038</v>
+      </c>
+      <c r="Y33" s="17">
         <f t="shared" si="4"/>
-        <v>2062</v>
-      </c>
-      <c r="S33" s="17">
-        <f t="shared" si="4"/>
-        <v>2038</v>
-      </c>
-      <c r="T33" s="17">
-        <f t="shared" si="4"/>
-        <v>2038</v>
-      </c>
-      <c r="V33" s="17">
-        <f t="shared" si="5"/>
         <v>2084</v>
       </c>
     </row>
-    <row r="34" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:25" x14ac:dyDescent="0.25">
       <c r="G34" s="12">
         <v>5</v>
       </c>
@@ -9032,24 +9202,31 @@
       <c r="K34" s="12">
         <v>5</v>
       </c>
-      <c r="R34" s="12">
+      <c r="L34" s="56">
+        <v>1</v>
+      </c>
+      <c r="M34" s="56">
+        <v>1</v>
+      </c>
+      <c r="N34" s="56"/>
+      <c r="U34" s="12">
+        <f>+U33+G34</f>
+        <v>2067</v>
+      </c>
+      <c r="V34" s="17">
+        <f>+V33+H34</f>
+        <v>2039</v>
+      </c>
+      <c r="W34" s="17">
+        <f>+W33+I34</f>
+        <v>2039</v>
+      </c>
+      <c r="Y34" s="17">
         <f t="shared" si="4"/>
-        <v>2067</v>
-      </c>
-      <c r="S34" s="17">
-        <f t="shared" si="4"/>
-        <v>2039</v>
-      </c>
-      <c r="T34" s="17">
-        <f t="shared" si="4"/>
-        <v>2039</v>
-      </c>
-      <c r="V34" s="17">
-        <f t="shared" si="5"/>
         <v>2089</v>
       </c>
     </row>
-    <row r="35" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:25" x14ac:dyDescent="0.25">
       <c r="G35" s="12">
         <v>5</v>
       </c>
@@ -9062,24 +9239,31 @@
       <c r="K35" s="12">
         <v>5</v>
       </c>
-      <c r="R35" s="12">
+      <c r="L35" s="56">
+        <v>1</v>
+      </c>
+      <c r="M35" s="56">
+        <v>1</v>
+      </c>
+      <c r="N35" s="56"/>
+      <c r="U35" s="12">
+        <f>+U34+G35</f>
+        <v>2072</v>
+      </c>
+      <c r="V35" s="17">
+        <f>+V34+H35</f>
+        <v>2040</v>
+      </c>
+      <c r="W35" s="17">
+        <f>+W34+I35</f>
+        <v>2040</v>
+      </c>
+      <c r="Y35" s="17">
         <f t="shared" si="4"/>
-        <v>2072</v>
-      </c>
-      <c r="S35" s="17">
-        <f t="shared" si="4"/>
-        <v>2040</v>
-      </c>
-      <c r="T35" s="17">
-        <f t="shared" si="4"/>
-        <v>2040</v>
-      </c>
-      <c r="V35" s="17">
-        <f t="shared" si="5"/>
         <v>2094</v>
       </c>
     </row>
-    <row r="36" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:25" x14ac:dyDescent="0.25">
       <c r="H36" s="17">
         <v>1</v>
       </c>
@@ -9089,216 +9273,514 @@
       <c r="K36" s="12">
         <v>5</v>
       </c>
-      <c r="S36" s="17">
-        <f t="shared" si="4"/>
+      <c r="L36" s="56">
+        <v>1</v>
+      </c>
+      <c r="M36" s="56">
+        <v>1</v>
+      </c>
+      <c r="N36" s="56"/>
+      <c r="V36" s="17">
+        <f t="shared" ref="V36:V45" si="5">+V35+H36</f>
         <v>2041</v>
       </c>
-      <c r="T36" s="17">
-        <f t="shared" si="4"/>
+      <c r="W36" s="17">
+        <f t="shared" ref="W36:W45" si="6">+W35+I36</f>
         <v>2041</v>
       </c>
-      <c r="V36" s="17">
-        <f>+V35+K36</f>
+      <c r="Y36" s="17">
+        <f>+Y35+K36</f>
         <v>2099</v>
       </c>
     </row>
-    <row r="37" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:25" x14ac:dyDescent="0.25">
       <c r="H37" s="17">
         <v>1</v>
       </c>
       <c r="I37" s="17">
         <v>1</v>
       </c>
-      <c r="S37" s="17">
-        <f t="shared" si="4"/>
+      <c r="L37" s="56">
+        <v>1</v>
+      </c>
+      <c r="M37" s="56">
+        <v>1</v>
+      </c>
+      <c r="N37" s="56"/>
+      <c r="V37" s="17">
+        <f t="shared" si="5"/>
         <v>2042</v>
       </c>
-      <c r="T37" s="17">
-        <f t="shared" si="4"/>
+      <c r="W37" s="17">
+        <f t="shared" si="6"/>
         <v>2042</v>
       </c>
     </row>
-    <row r="38" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:25" x14ac:dyDescent="0.25">
       <c r="H38" s="17">
         <v>1</v>
       </c>
       <c r="I38" s="17">
         <v>1</v>
       </c>
-      <c r="S38" s="17">
-        <f t="shared" si="4"/>
+      <c r="L38" s="56">
+        <v>1</v>
+      </c>
+      <c r="M38" s="56">
+        <v>1</v>
+      </c>
+      <c r="N38" s="56"/>
+      <c r="V38" s="17">
+        <f t="shared" si="5"/>
         <v>2043</v>
       </c>
-      <c r="T38" s="17">
-        <f t="shared" si="4"/>
+      <c r="W38" s="17">
+        <f t="shared" si="6"/>
         <v>2043</v>
       </c>
     </row>
-    <row r="39" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:25" x14ac:dyDescent="0.25">
       <c r="H39" s="17">
         <v>1</v>
       </c>
       <c r="I39" s="17">
         <v>1</v>
       </c>
-      <c r="S39" s="17">
-        <f t="shared" si="4"/>
+      <c r="L39" s="56">
+        <v>1</v>
+      </c>
+      <c r="M39" s="56">
+        <v>1</v>
+      </c>
+      <c r="N39" s="56"/>
+      <c r="V39" s="17">
+        <f t="shared" si="5"/>
         <v>2044</v>
       </c>
-      <c r="T39" s="17">
-        <f t="shared" si="4"/>
+      <c r="W39" s="17">
+        <f t="shared" si="6"/>
         <v>2044</v>
       </c>
     </row>
-    <row r="40" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:25" x14ac:dyDescent="0.25">
       <c r="H40" s="17">
         <v>1</v>
       </c>
       <c r="I40" s="17">
         <v>1</v>
       </c>
-      <c r="S40" s="17">
-        <f t="shared" si="4"/>
+      <c r="L40" s="56">
+        <v>1</v>
+      </c>
+      <c r="M40" s="56">
+        <v>1</v>
+      </c>
+      <c r="N40" s="56"/>
+      <c r="V40" s="17">
+        <f t="shared" si="5"/>
         <v>2045</v>
       </c>
-      <c r="T40" s="17">
-        <f t="shared" si="4"/>
+      <c r="W40" s="17">
+        <f t="shared" si="6"/>
         <v>2045</v>
       </c>
     </row>
-    <row r="41" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:25" x14ac:dyDescent="0.25">
       <c r="H41" s="17">
         <v>1</v>
       </c>
       <c r="I41" s="17">
         <v>1</v>
       </c>
-      <c r="S41" s="17">
-        <f t="shared" si="4"/>
+      <c r="L41" s="56">
+        <v>1</v>
+      </c>
+      <c r="M41" s="56">
+        <v>1</v>
+      </c>
+      <c r="N41" s="56"/>
+      <c r="V41" s="17">
+        <f t="shared" si="5"/>
         <v>2046</v>
       </c>
-      <c r="T41" s="17">
-        <f t="shared" si="4"/>
+      <c r="W41" s="17">
+        <f t="shared" si="6"/>
         <v>2046</v>
       </c>
     </row>
-    <row r="42" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:25" x14ac:dyDescent="0.25">
       <c r="H42" s="17">
         <v>1</v>
       </c>
       <c r="I42" s="17">
         <v>1</v>
       </c>
-      <c r="S42" s="17">
-        <f t="shared" si="4"/>
+      <c r="L42" s="56">
+        <v>1</v>
+      </c>
+      <c r="M42" s="56">
+        <v>1</v>
+      </c>
+      <c r="N42" s="56"/>
+      <c r="V42" s="17">
+        <f t="shared" si="5"/>
         <v>2047</v>
       </c>
-      <c r="T42" s="17">
-        <f t="shared" si="4"/>
+      <c r="W42" s="17">
+        <f t="shared" si="6"/>
         <v>2047</v>
       </c>
     </row>
-    <row r="43" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:25" x14ac:dyDescent="0.25">
       <c r="H43" s="17">
         <v>1</v>
       </c>
       <c r="I43" s="17">
         <v>1</v>
       </c>
-      <c r="S43" s="17">
-        <f t="shared" si="4"/>
+      <c r="L43" s="56">
+        <v>1</v>
+      </c>
+      <c r="M43" s="56">
+        <v>1</v>
+      </c>
+      <c r="N43" s="56"/>
+      <c r="V43" s="17">
+        <f t="shared" si="5"/>
         <v>2048</v>
       </c>
-      <c r="T43" s="17">
-        <f t="shared" si="4"/>
+      <c r="W43" s="17">
+        <f t="shared" si="6"/>
         <v>2048</v>
       </c>
     </row>
-    <row r="44" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:25" x14ac:dyDescent="0.25">
       <c r="H44" s="17">
         <v>1</v>
       </c>
       <c r="I44" s="17">
         <v>1</v>
       </c>
-      <c r="S44" s="17">
-        <f t="shared" si="4"/>
+      <c r="L44" s="56">
+        <v>1</v>
+      </c>
+      <c r="M44" s="56">
+        <v>1</v>
+      </c>
+      <c r="N44" s="56"/>
+      <c r="V44" s="17">
+        <f t="shared" si="5"/>
         <v>2049</v>
       </c>
-      <c r="T44" s="17">
-        <f t="shared" si="4"/>
+      <c r="W44" s="17">
+        <f t="shared" si="6"/>
         <v>2049</v>
       </c>
     </row>
-    <row r="45" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:25" x14ac:dyDescent="0.25">
       <c r="H45" s="17">
         <v>1</v>
       </c>
       <c r="I45" s="17">
         <v>1</v>
       </c>
-      <c r="S45" s="17">
-        <f t="shared" si="4"/>
+      <c r="L45" s="56">
+        <v>1</v>
+      </c>
+      <c r="M45" s="56">
+        <v>1</v>
+      </c>
+      <c r="N45" s="56"/>
+      <c r="V45" s="17">
+        <f t="shared" si="5"/>
         <v>2050</v>
       </c>
-      <c r="T45" s="17">
-        <f t="shared" si="4"/>
+      <c r="W45" s="17">
+        <f t="shared" si="6"/>
         <v>2050</v>
       </c>
     </row>
-    <row r="46" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:25" x14ac:dyDescent="0.25">
       <c r="I46" s="17">
         <v>1</v>
       </c>
-      <c r="T46" s="17">
-        <f>+T45+I46</f>
+      <c r="L46" s="56">
+        <v>1</v>
+      </c>
+      <c r="M46" s="56">
+        <v>1</v>
+      </c>
+      <c r="N46" s="56"/>
+      <c r="W46" s="17">
+        <f>+W45+I46</f>
         <v>2051</v>
       </c>
     </row>
-    <row r="47" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:25" x14ac:dyDescent="0.25">
       <c r="I47" s="17">
         <v>1</v>
       </c>
-      <c r="T47" s="17">
-        <f>+T46+I47</f>
+      <c r="L47" s="56">
+        <v>1</v>
+      </c>
+      <c r="M47" s="56">
+        <v>1</v>
+      </c>
+      <c r="N47" s="56"/>
+      <c r="W47" s="17">
+        <f>+W46+I47</f>
         <v>2052</v>
       </c>
     </row>
-    <row r="48" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:25" x14ac:dyDescent="0.25">
       <c r="I48" s="17">
         <v>5</v>
       </c>
-      <c r="T48" s="17">
-        <f>+T47+I48-2</f>
+      <c r="L48" s="56">
+        <v>1</v>
+      </c>
+      <c r="M48" s="56">
+        <v>1</v>
+      </c>
+      <c r="N48" s="56"/>
+      <c r="W48" s="17">
+        <f>+W47+I48-2</f>
         <v>2055</v>
       </c>
     </row>
-    <row r="49" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="9:23" x14ac:dyDescent="0.25">
       <c r="I49" s="17">
         <v>5</v>
       </c>
-      <c r="T49" s="17">
-        <f t="shared" ref="T49:T51" si="6">+T48+I49</f>
+      <c r="L49" s="56">
+        <v>1</v>
+      </c>
+      <c r="M49" s="56">
+        <v>1</v>
+      </c>
+      <c r="N49" s="56"/>
+      <c r="W49" s="17">
+        <f t="shared" ref="W49:W51" si="7">+W48+I49</f>
         <v>2060</v>
       </c>
     </row>
-    <row r="50" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="9:23" x14ac:dyDescent="0.25">
       <c r="I50" s="17">
         <v>5</v>
       </c>
-      <c r="T50" s="17">
-        <f t="shared" si="6"/>
+      <c r="L50" s="56">
+        <v>1</v>
+      </c>
+      <c r="M50" s="56">
+        <v>1</v>
+      </c>
+      <c r="N50" s="56"/>
+      <c r="W50" s="17">
+        <f t="shared" si="7"/>
         <v>2065</v>
       </c>
     </row>
-    <row r="51" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="9:23" x14ac:dyDescent="0.25">
       <c r="I51" s="17">
         <v>5</v>
       </c>
-      <c r="T51" s="17">
-        <f t="shared" si="6"/>
+      <c r="L51" s="56">
+        <v>1</v>
+      </c>
+      <c r="M51" s="56">
+        <v>1</v>
+      </c>
+      <c r="N51" s="56"/>
+      <c r="W51" s="17">
+        <f t="shared" si="7"/>
         <v>2070</v>
       </c>
+    </row>
+    <row r="52" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L52" s="56">
+        <v>1</v>
+      </c>
+      <c r="M52" s="56">
+        <v>1</v>
+      </c>
+      <c r="N52" s="56"/>
+    </row>
+    <row r="53" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L53" s="56">
+        <v>1</v>
+      </c>
+      <c r="M53" s="56">
+        <v>1</v>
+      </c>
+      <c r="N53" s="56"/>
+    </row>
+    <row r="54" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L54" s="56">
+        <v>1</v>
+      </c>
+      <c r="M54" s="56">
+        <v>1</v>
+      </c>
+      <c r="N54" s="56"/>
+    </row>
+    <row r="55" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L55" s="56">
+        <v>1</v>
+      </c>
+      <c r="M55" s="56">
+        <v>1</v>
+      </c>
+      <c r="N55" s="56"/>
+    </row>
+    <row r="56" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L56" s="56">
+        <v>1</v>
+      </c>
+      <c r="M56" s="56">
+        <v>1</v>
+      </c>
+      <c r="N56" s="56"/>
+    </row>
+    <row r="57" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L57" s="56">
+        <v>1</v>
+      </c>
+      <c r="M57" s="56">
+        <v>1</v>
+      </c>
+      <c r="N57" s="56"/>
+    </row>
+    <row r="58" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L58" s="56">
+        <v>1</v>
+      </c>
+      <c r="M58" s="56">
+        <v>1</v>
+      </c>
+      <c r="N58" s="56"/>
+    </row>
+    <row r="59" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L59" s="56">
+        <v>1</v>
+      </c>
+      <c r="M59" s="56">
+        <v>1</v>
+      </c>
+      <c r="N59" s="56"/>
+    </row>
+    <row r="60" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L60" s="56">
+        <v>1</v>
+      </c>
+      <c r="M60" s="56">
+        <v>1</v>
+      </c>
+      <c r="N60" s="56"/>
+    </row>
+    <row r="61" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L61" s="56">
+        <v>1</v>
+      </c>
+      <c r="M61" s="56">
+        <v>1</v>
+      </c>
+      <c r="N61" s="56"/>
+    </row>
+    <row r="62" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L62" s="56">
+        <v>1</v>
+      </c>
+      <c r="M62" s="56">
+        <v>1</v>
+      </c>
+      <c r="N62" s="56"/>
+    </row>
+    <row r="63" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L63" s="56">
+        <v>1</v>
+      </c>
+      <c r="M63" s="56">
+        <v>1</v>
+      </c>
+      <c r="N63" s="56"/>
+    </row>
+    <row r="64" spans="9:23" x14ac:dyDescent="0.25">
+      <c r="L64" s="56">
+        <v>1</v>
+      </c>
+      <c r="M64" s="56">
+        <v>1</v>
+      </c>
+      <c r="N64" s="56"/>
+    </row>
+    <row r="65" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L65" s="56">
+        <v>1</v>
+      </c>
+      <c r="M65" s="56">
+        <v>1</v>
+      </c>
+      <c r="N65" s="56"/>
+    </row>
+    <row r="66" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="M66" s="56">
+        <v>1</v>
+      </c>
+      <c r="N66" s="56"/>
+    </row>
+    <row r="67" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="M67" s="56">
+        <v>1</v>
+      </c>
+      <c r="N67" s="56"/>
+    </row>
+    <row r="68" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="M68" s="56">
+        <v>1</v>
+      </c>
+      <c r="N68" s="56"/>
+    </row>
+    <row r="69" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="M69" s="56">
+        <v>1</v>
+      </c>
+      <c r="N69" s="56"/>
+    </row>
+    <row r="70" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="M70" s="56">
+        <v>1</v>
+      </c>
+      <c r="N70" s="56"/>
+    </row>
+    <row r="71" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="M71" s="56">
+        <v>1</v>
+      </c>
+      <c r="N71" s="56"/>
+    </row>
+    <row r="72" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="M72" s="56">
+        <v>1</v>
+      </c>
+      <c r="N72" s="56"/>
+    </row>
+    <row r="73" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="M73" s="56">
+        <v>1</v>
+      </c>
+      <c r="N73" s="56"/>
+    </row>
+    <row r="74" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="M74" s="56">
+        <v>1</v>
+      </c>
+      <c r="N74" s="56"/>
+    </row>
+    <row r="75" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="M75" s="56">
+        <v>1</v>
+      </c>
+      <c r="N75" s="56"/>
     </row>
   </sheetData>
   <phoneticPr fontId="27" type="noConversion"/>
@@ -9314,7 +9796,7 @@
   <dimension ref="B3:C9"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="52.6328125" customWidth="1"/>
+    <col min="2" max="2" width="52.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:3" ht="13" x14ac:dyDescent="0.3">
@@ -9380,14 +9862,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" customWidth="1"/>
-    <col min="7" max="7" width="6.453125" customWidth="1"/>
-    <col min="8" max="8" width="6.36328125" customWidth="1"/>
-    <col min="12" max="12" width="9.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" customWidth="1"/>
+    <col min="7" max="8" width="6.453125" customWidth="1"/>
+    <col min="10" max="10" width="23.36328125" customWidth="1"/>
+    <col min="12" max="12" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -9784,7 +10266,7 @@
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
       <c r="J22" s="24" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K22" s="24"/>
       <c r="L22" s="24"/>
@@ -9810,7 +10292,7 @@
       <c r="H23" s="24"/>
       <c r="I23" s="24"/>
       <c r="J23" s="24" t="s">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="K23" s="24"/>
       <c r="L23" s="24"/>
@@ -9822,20 +10304,35 @@
     <row r="24" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" s="24"/>
       <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
+      <c r="C24" s="24" t="s">
+        <v>164</v>
+      </c>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
+      <c r="F24" s="24">
+        <v>0</v>
+      </c>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
+      <c r="J24" s="24" t="s">
+        <v>171</v>
+      </c>
       <c r="K24" s="24"/>
       <c r="L24" s="24"/>
       <c r="M24" s="24"/>
       <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
       <c r="P24" s="24"/>
+    </row>
+    <row r="29" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+      <c r="B29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="I29" s="24"/>
+    </row>
+    <row r="30" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+      <c r="B30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="I30" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9850,10 +10347,10 @@
   <dimension ref="B1:G34"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.08984375" customWidth="1"/>
-    <col min="3" max="3" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="6.08984375" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" customWidth="1"/>
     <col min="6" max="6" width="17.54296875" customWidth="1"/>
     <col min="7" max="7" width="10.453125" customWidth="1"/>
   </cols>
@@ -10284,57 +10781,6 @@
         <v>0.95079986728164989</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="C28" s="7" t="str">
-        <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B25,4))</f>
-        <v>MEUR2022</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="G28" s="25">
-        <f>CPI!$D$21/CPI!D25</f>
-        <v>0.87069584915901999</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="C29" s="7" t="str">
-        <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B26,4))</f>
-        <v>MEUR2023</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="G29" s="25">
-        <f>CPI!$D$21/CPI!D26</f>
-        <v>0.81832316650283832</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="C30" s="7" t="str">
-        <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B27,4))</f>
-        <v>MEUR2024</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="G30" s="25">
-        <f>CPI!$D$21/CPI!D27</f>
-        <v>0.79758593226397489</v>
-      </c>
-    </row>
     <row r="31" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B31" s="7"/>
     </row>
@@ -10348,7 +10794,6 @@
       <c r="B34" s="25"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -10358,7 +10803,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="B2:O29"/>
+  <dimension ref="B2:O25"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="15.54296875" customWidth="1"/>
@@ -10696,27 +11141,6 @@
         <f>Constants!C27</f>
         <v>MEUR2021</v>
       </c>
-    </row>
-    <row r="26" spans="2:2" ht="13" x14ac:dyDescent="0.3">
-      <c r="B26" s="7" t="str">
-        <f>Constants!C28</f>
-        <v>MEUR2022</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" ht="13" x14ac:dyDescent="0.3">
-      <c r="B27" s="7" t="str">
-        <f>Constants!C29</f>
-        <v>MEUR2023</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" ht="13" x14ac:dyDescent="0.3">
-      <c r="B28" s="7" t="str">
-        <f>Constants!C30</f>
-        <v>MEUR2024</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" ht="13" x14ac:dyDescent="0.3">
-      <c r="B29" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10728,11 +11152,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="B2:D32"/>
+  <dimension ref="B2:D26"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.453125" customWidth="1"/>
-    <col min="3" max="4" width="13.90625" customWidth="1"/>
+    <col min="3" max="4" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11005,54 +11429,8 @@
         <v>146.47319386728233</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="B25" s="36">
-        <v>2022</v>
-      </c>
-      <c r="C25" s="38">
-        <v>9.1999999999999998E-2</v>
-      </c>
-      <c r="D25" s="37">
-        <f t="shared" ref="D25:D27" si="3">D24+D24*C25</f>
-        <v>159.94872770307231</v>
-      </c>
-    </row>
     <row r="26" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="B26" s="36">
-        <v>2023</v>
-      </c>
-      <c r="C26" s="38">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="D26" s="37">
-        <f t="shared" si="3"/>
-        <v>170.18544627606894</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="B27" s="36">
-        <v>2024</v>
-      </c>
-      <c r="C27" s="38">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="D27" s="37">
-        <f t="shared" si="3"/>
-        <v>174.61026787924675</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="B28" s="36"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="37"/>
-    </row>
-    <row r="29" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="B29" s="36"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="37"/>
-    </row>
-    <row r="32" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="B32" s="35" t="s">
+      <c r="B26" s="35" t="s">
         <v>36</v>
       </c>
     </row>
